--- a/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_RV__RV_Mean.xlsx
+++ b/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_RV__RV_Mean.xlsx
@@ -381,689 +381,689 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.7118227867565571</v>
+        <v>0.7565807590943172</v>
       </c>
       <c r="C2">
-        <v>0.5787519551646474</v>
+        <v>0.8038403951702461</v>
       </c>
       <c r="D2">
-        <v>0.3393538379696547</v>
+        <v>0.4647915684760843</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.652166176071628</v>
+        <v>0.8161678283801553</v>
       </c>
       <c r="C3">
-        <v>0.6104822318228487</v>
+        <v>0.8015622626077564</v>
       </c>
       <c r="D3">
-        <v>0.3637899708702775</v>
+        <v>0.5775323077649911</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.7753906577797243</v>
+        <v>0.7155239843057362</v>
       </c>
       <c r="C4">
-        <v>0.7582853086208171</v>
+        <v>0.6232440868592279</v>
       </c>
       <c r="D4">
-        <v>0.5636648999110929</v>
+        <v>0.3988259807667701</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.7431131793909721</v>
+        <v>0.9822888888888889</v>
       </c>
       <c r="C5">
-        <v>0.7624851499201979</v>
+        <v>0.8773692621010294</v>
       </c>
       <c r="D5">
-        <v>0.5142650533161018</v>
+        <v>0.7374173968588268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.7155239843057362</v>
+        <v>0.6341548106726145</v>
       </c>
       <c r="C6">
-        <v>0.6232440868592279</v>
+        <v>0.6034813078976664</v>
       </c>
       <c r="D6">
-        <v>0.3988259807667701</v>
+        <v>0.3773652237377098</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.8161678283801553</v>
+        <v>0.9968111111111111</v>
       </c>
       <c r="C7">
-        <v>0.8015622626077564</v>
+        <v>0.8883231986945382</v>
       </c>
       <c r="D7">
-        <v>0.5775323077649911</v>
+        <v>0.6614019652438208</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.9488161674835511</v>
+        <v>0.8276420112337894</v>
       </c>
       <c r="C8">
-        <v>0.8711512603696795</v>
+        <v>0.827202821597928</v>
       </c>
       <c r="D8">
-        <v>0.6973067303874012</v>
+        <v>0.636169432181516</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.6484822840829647</v>
+        <v>0.9920151034548518</v>
       </c>
       <c r="C9">
-        <v>0.7003541764288356</v>
+        <v>0.8457551739145437</v>
       </c>
       <c r="D9">
-        <v>0.3263145353341117</v>
+        <v>0.7515845298860258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.8645659279597145</v>
+        <v>0.7137259740906082</v>
       </c>
       <c r="C10">
-        <v>0.7515197660815023</v>
+        <v>0.580818074420597</v>
       </c>
       <c r="D10">
-        <v>0.6417321024943941</v>
+        <v>0.3529901931494545</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.9968111111111111</v>
+        <v>0.7118227867565571</v>
       </c>
       <c r="C11">
-        <v>0.8883231986945382</v>
+        <v>0.5787519551646474</v>
       </c>
       <c r="D11">
-        <v>0.6614019652438208</v>
+        <v>0.3393538379696547</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.6341548106726145</v>
+        <v>0.8075472260524486</v>
       </c>
       <c r="C12">
-        <v>0.6034813078976664</v>
+        <v>0.6572383582235283</v>
       </c>
       <c r="D12">
-        <v>0.3773652237377098</v>
+        <v>0.474892690605162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.7565807590943172</v>
+        <v>0.6809800076303848</v>
       </c>
       <c r="C13">
-        <v>0.8038403951702461</v>
+        <v>0.6049876156202627</v>
       </c>
       <c r="D13">
-        <v>0.4647915684760843</v>
+        <v>0.3619060790313545</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.9908111111111111</v>
+        <v>0.6080771042963408</v>
       </c>
       <c r="C14">
-        <v>0.6000203192341012</v>
+        <v>0.6012241745227438</v>
       </c>
       <c r="D14">
-        <v>0.4941387119927211</v>
+        <v>0.3242817700417596</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.9973628637750958</v>
+        <v>0.5948173666556785</v>
       </c>
       <c r="C15">
-        <v>0.6162174988152724</v>
+        <v>0.5201015555634853</v>
       </c>
       <c r="D15">
-        <v>0.5820335620211351</v>
+        <v>0.2990541252367934</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B16">
-        <v>1.0646</v>
+        <v>0.6484822840829647</v>
       </c>
       <c r="C16">
-        <v>0.4974135525870444</v>
+        <v>0.7003541764288356</v>
       </c>
       <c r="D16">
-        <v>0.4496826417812644</v>
+        <v>0.3263145353341117</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B17">
-        <v>1.005088888888889</v>
+        <v>0.7214190863358046</v>
       </c>
       <c r="C17">
-        <v>0.9109340527183041</v>
+        <v>0.5041851318273137</v>
       </c>
       <c r="D17">
-        <v>0.6502119074089877</v>
+        <v>0.3683042246966088</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.7137259740906082</v>
+        <v>0.5653969383434816</v>
       </c>
       <c r="C18">
-        <v>0.580818074420597</v>
+        <v>0.5352292813341586</v>
       </c>
       <c r="D18">
-        <v>0.3529901931494545</v>
+        <v>0.3608720881963459</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.6577372465434015</v>
+        <v>0.9881444444444445</v>
       </c>
       <c r="C19">
-        <v>0.6316785852416488</v>
+        <v>0.9500530372052602</v>
       </c>
       <c r="D19">
-        <v>0.3423906222664039</v>
+        <v>0.8381947420382349</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.5790462336609022</v>
+        <v>0.9946038156535486</v>
       </c>
       <c r="C20">
-        <v>0.5364698565481983</v>
+        <v>0.9807</v>
       </c>
       <c r="D20">
-        <v>0.2988156123930447</v>
+        <v>0.5998650622987863</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.6384465164236864</v>
+        <v>0.7246002640071652</v>
       </c>
       <c r="C21">
-        <v>0.5849188726661088</v>
+        <v>0.6576176603772614</v>
       </c>
       <c r="D21">
-        <v>0.304520502750728</v>
+        <v>0.4681788228081814</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.8075472260524486</v>
+        <v>0.8645659279597145</v>
       </c>
       <c r="C22">
-        <v>0.6572383582235283</v>
+        <v>0.7515197660815023</v>
       </c>
       <c r="D22">
-        <v>0.474892690605162</v>
+        <v>0.6417321024943941</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.8276420112337894</v>
+        <v>0.7753906577797243</v>
       </c>
       <c r="C23">
-        <v>0.827202821597928</v>
+        <v>0.7582853086208171</v>
       </c>
       <c r="D23">
-        <v>0.636169432181516</v>
+        <v>0.5636648999110929</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.8578388213773234</v>
+        <v>1.005088888888889</v>
       </c>
       <c r="C24">
-        <v>0.4844828701036129</v>
+        <v>0.9109340527183041</v>
       </c>
       <c r="D24">
-        <v>0.3128644856450556</v>
+        <v>0.6502119074089877</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.577627042624638</v>
+        <v>0.81125244960816</v>
       </c>
       <c r="C25">
-        <v>0.5237135292160039</v>
+        <v>0.780690062605083</v>
       </c>
       <c r="D25">
-        <v>0.4152826581420878</v>
+        <v>0.5353348357635287</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.6673387928587692</v>
+        <v>0.9533945717232737</v>
       </c>
       <c r="C26">
-        <v>0.5692325941998699</v>
+        <v>0.9428381564674454</v>
       </c>
       <c r="D26">
-        <v>0.3499009385853212</v>
+        <v>0.8497070129887914</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.6148306573834882</v>
+        <v>0.7431131793909721</v>
       </c>
       <c r="C27">
-        <v>0.4630590320149452</v>
+        <v>0.7624851499201979</v>
       </c>
       <c r="D27">
-        <v>0.2478195326261151</v>
+        <v>0.5142650533161018</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.81125244960816</v>
+        <v>0.6673387928587692</v>
       </c>
       <c r="C28">
-        <v>0.780690062605083</v>
+        <v>0.5692325941998699</v>
       </c>
       <c r="D28">
-        <v>0.5353348357635287</v>
+        <v>0.3499009385853212</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.9533945717232737</v>
+        <v>0.9973628637750958</v>
       </c>
       <c r="C29">
-        <v>0.9428381564674454</v>
+        <v>0.6162174988152724</v>
       </c>
       <c r="D29">
-        <v>0.8497070129887914</v>
+        <v>0.5820335620211351</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.6809800076303848</v>
+        <v>0.6917635979632824</v>
       </c>
       <c r="C30">
-        <v>0.6049876156202627</v>
+        <v>0.5759229338784446</v>
       </c>
       <c r="D30">
-        <v>0.3619060790313545</v>
+        <v>0.3594554108375438</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.6080771042963408</v>
+        <v>0.9488161674835511</v>
       </c>
       <c r="C31">
-        <v>0.6012241745227438</v>
+        <v>0.8711512603696795</v>
       </c>
       <c r="D31">
-        <v>0.3242817700417596</v>
+        <v>0.6973067303874012</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.5653969383434816</v>
+        <v>0.5567701525989879</v>
       </c>
       <c r="C32">
-        <v>0.5352292813341586</v>
+        <v>0.5982026524700186</v>
       </c>
       <c r="D32">
-        <v>0.3608720881963459</v>
+        <v>0.3305842851368141</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.6917635979632824</v>
+        <v>0.6577372465434015</v>
       </c>
       <c r="C33">
-        <v>0.5759229338784446</v>
+        <v>0.6316785852416488</v>
       </c>
       <c r="D33">
-        <v>0.3594554108375438</v>
+        <v>0.3423906222664039</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.7065906586260827</v>
+        <v>0.9908111111111111</v>
       </c>
       <c r="C34">
-        <v>0.6546639009039917</v>
+        <v>0.6000203192341012</v>
       </c>
       <c r="D34">
-        <v>0.4840906105543578</v>
+        <v>0.4941387119927211</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.5567701525989879</v>
+        <v>0.6384465164236864</v>
       </c>
       <c r="C35">
-        <v>0.5982026524700186</v>
+        <v>0.5849188726661088</v>
       </c>
       <c r="D35">
-        <v>0.3305842851368141</v>
+        <v>0.304520502750728</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.5948173666556785</v>
+        <v>0.652166176071628</v>
       </c>
       <c r="C36">
-        <v>0.5201015555634853</v>
+        <v>0.6104822318228487</v>
       </c>
       <c r="D36">
-        <v>0.2990541252367934</v>
+        <v>0.3637899708702775</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.9946038156535486</v>
+        <v>0.7065906586260827</v>
       </c>
       <c r="C37">
-        <v>0.9807</v>
+        <v>0.6546639009039917</v>
       </c>
       <c r="D37">
-        <v>0.5998650622987863</v>
+        <v>0.4840906105543578</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.9881444444444445</v>
+        <v>1.0646</v>
       </c>
       <c r="C38">
-        <v>0.9500530372052602</v>
+        <v>0.4974135525870444</v>
       </c>
       <c r="D38">
-        <v>0.8381947420382349</v>
+        <v>0.4496826417812644</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.7231915395827178</v>
+        <v>0.8914118915878219</v>
       </c>
       <c r="C39">
-        <v>0.6516136086143469</v>
+        <v>0.8387399199875736</v>
       </c>
       <c r="D39">
-        <v>0.4725484362492473</v>
+        <v>0.6373239545604206</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.8914118915878219</v>
+        <v>0.8578388213773234</v>
       </c>
       <c r="C40">
-        <v>0.8387399199875736</v>
+        <v>0.4844828701036129</v>
       </c>
       <c r="D40">
-        <v>0.6373239545604206</v>
+        <v>0.3128644856450556</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.7214190863358046</v>
+        <v>0.7231915395827178</v>
       </c>
       <c r="C41">
-        <v>0.5041851318273137</v>
+        <v>0.6516136086143469</v>
       </c>
       <c r="D41">
-        <v>0.3683042246966088</v>
+        <v>0.4725484362492473</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.9822888888888889</v>
+        <v>0.5790462336609022</v>
       </c>
       <c r="C42">
-        <v>0.8773692621010294</v>
+        <v>0.5364698565481983</v>
       </c>
       <c r="D42">
-        <v>0.7374173968588268</v>
+        <v>0.2988156123930447</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.7246002640071652</v>
+        <v>0.577627042624638</v>
       </c>
       <c r="C43">
-        <v>0.6576176603772614</v>
+        <v>0.5237135292160039</v>
       </c>
       <c r="D43">
-        <v>0.4681788228081814</v>
+        <v>0.4152826581420878</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.9920151034548518</v>
+        <v>0.6148306573834882</v>
       </c>
       <c r="C44">
-        <v>0.8457551739145437</v>
+        <v>0.4630590320149452</v>
       </c>
       <c r="D44">
-        <v>0.7515845298860258</v>
+        <v>0.2478195326261151</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +1091,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
